--- a/AAII_Financials/Quarterly/NOVA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NOVA_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="92">
   <si>
     <t>NOVA</t>
   </si>
@@ -656,353 +656,365 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>194200</v>
+      </c>
+      <c r="E8" s="3">
         <v>198400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>166400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>161700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>195600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>149400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>147000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>65700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>65000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>68900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>66600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>41300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>38000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>50200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>42800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>29800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>33600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>36600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>34600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>26700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>25200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>30400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>29000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>19800</v>
       </c>
-      <c r="AA8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>124600</v>
+      </c>
+      <c r="E9" s="3">
         <v>115400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>88300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>99200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>134300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>81100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>82100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>29500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>29100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>27000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>23500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>18600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>17700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>16500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>16900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>14000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>13700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>12100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>11300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>10300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>9800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>10000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>8700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>8300</v>
       </c>
-      <c r="AA9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>69600</v>
+      </c>
+      <c r="E10" s="3">
         <v>83000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>78100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>62500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>61300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>68300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>64900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>36200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>35900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>41900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>43100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>22700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>20300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>33700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>25900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>15800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>19900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>24500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>23300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>16400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>15400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>20400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>20300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>11500</v>
       </c>
-      <c r="AA10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1030,8 +1042,9 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1107,8 +1120,11 @@
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1184,13 +1200,16 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>13200</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -1198,71 +1217,74 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>1200</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>9800</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
         <v>92100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>50700</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>10600</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>3</v>
+      <c r="Z14" s="3">
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1338,8 +1360,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1364,162 +1389,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>290800</v>
+      </c>
+      <c r="E17" s="3">
         <v>236600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>226100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>210500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>212400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>177100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>149700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>99900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>74100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>77100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>90700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>64600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>148100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>99200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>47900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>44100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>42800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>42500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>48000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>31200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>37600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>27000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>26500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>26900</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-96600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-38200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-59700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-48800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-16800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-27700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-34200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-9100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-8200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-24100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-23300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-110100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-49000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-5100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-14300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-9200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-5900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-13400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-4500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-12400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-7100</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1547,334 +1579,347 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>34200</v>
+      </c>
+      <c r="E20" s="3">
         <v>30000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>23100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>24500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>22100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>16200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>13500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>12100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>9500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>8900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>8000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>7300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>8000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>5900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>6900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>4600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>3600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>3100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>2400</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>1800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1400</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="E21" s="3">
         <v>39000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>5700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>15600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>42200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>23200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>43900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>9800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>31000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>29700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>11700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-83800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-26200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>17700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>5300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>8800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>9600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>6500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-2000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>15800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>13300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1800</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>171800</v>
+      </c>
+      <c r="E22" s="3">
         <v>57600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>56900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>85600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>71500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>20800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>24600</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
       <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
         <v>31500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>26600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>50100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>8100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>26800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>30000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>30500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>67300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>8200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>31600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>38900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>31000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>26700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>11800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>13100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>6300</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-234200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-65800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-93600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-109800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-66200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-32300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-13800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-22100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-31100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-25900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-66300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-24100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-128800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-73100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-28700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-77000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-13800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-34400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-49800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-35500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-39100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-6600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-9200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-13400</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>600</v>
+      </c>
+      <c r="E24" s="3">
         <v>-9300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>7200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3900</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
         <v>0</v>
       </c>
@@ -1882,26 +1927,26 @@
         <v>0</v>
       </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>200</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
         <v>0</v>
       </c>
@@ -1932,8 +1977,11 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2009,162 +2057,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-234800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-56500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-100800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-110300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-70100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-32300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-13800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-22100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-31300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-25900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-66300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-24100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-128800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-73300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-28700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-77000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-13800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-34400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-49800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-35500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-39100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-6600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-9200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-13400</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-187600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-63100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-86100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-81100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-29000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-64500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-41100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-35100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-14200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-27500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-63400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-33000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-91800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-64200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-25300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-71100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-17500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-37600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-63300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-50700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-53000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-17900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-23300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-41700</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2240,8 +2297,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2317,8 +2377,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2394,8 +2457,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2471,162 +2537,171 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-34200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-30000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-23100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-24500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-22100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-16200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-13500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-12100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-9500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-8900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-8000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-7300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-8000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-6900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-4600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-3600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-3100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-2400</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-187600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-63100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-86100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-81100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-29000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-64500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-41100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-35100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-14200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-27500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-63400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-33000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-91800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-64200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-25300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-71100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-17500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-37600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-63300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-50700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-53000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-17900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-23300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-41700</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2702,167 +2777,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-187600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-63100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-86100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-81100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-29000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-64500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-41100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-35100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-14200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-27500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-63400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-33000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-91800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-64200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-25300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-71100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-17500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-37600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-63300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-50700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-53000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-17900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-23300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-41700</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2890,8 +2974,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2919,71 +3004,72 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>212800</v>
+      </c>
+      <c r="E41" s="3">
         <v>467900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>187300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>210900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>360300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>412600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>208100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>208500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>243100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>408200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>368600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>150900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>209900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>84600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>102300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>73400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>83500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>51000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>58800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>43900</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2996,8 +3082,11 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3073,71 +3162,74 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>478100</v>
+      </c>
+      <c r="E43" s="3">
         <v>315600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>301600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>355400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>358800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>289900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>227800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>145300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>139200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>95400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>78000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>63200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>56500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>46100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>37100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>35400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>31600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>29000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>26900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>20800</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3150,71 +3242,74 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>148600</v>
+      </c>
+      <c r="E44" s="3">
         <v>137700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>179200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>182900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>152100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>186600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>150700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>150500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>128000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>134900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>128000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>107700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>102600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>111000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>120800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>115100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>43700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>17100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>16500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>15800</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3227,71 +3322,74 @@
       <c r="AA44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>96700</v>
+      </c>
+      <c r="E45" s="3">
         <v>72800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>78600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>78900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>77200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>48300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>84100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>58300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>105500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>79300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>65100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>55000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>87700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>67700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>26600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>56000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>115500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>29300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>6800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>5500</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3304,71 +3402,74 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>936200</v>
+      </c>
+      <c r="E46" s="3">
         <v>993900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>746800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>828100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>948400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>937300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>670700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>562600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>615700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>717700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>639700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>376800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>456700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>309400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>286800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>280000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>274300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>126400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>109000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>86000</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3381,71 +3482,74 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3736000</v>
+      </c>
+      <c r="E47" s="3">
         <v>3531100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3228300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2864500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2466100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2072300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1736600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1450000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1204100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>962500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>773500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>622900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>513400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>428600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>379000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>338500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>298000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>255100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>223600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>197800</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3458,71 +3562,74 @@
       <c r="AA47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5656100</v>
+      </c>
+      <c r="E48" s="3">
         <v>5136400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4529100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4070900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3802000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3554800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3306100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3075200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2928300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2748300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2602300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2455000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2332300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2181700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2015300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1894000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1754700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1629900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1499900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1399300</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3535,44 +3642,47 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>134100</v>
+      </c>
+      <c r="E49" s="3">
         <v>154300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>161400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>168600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>175700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>182300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>189400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>196600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>203700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>210900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>204200</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3588,8 +3698,8 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T49" s="3">
-        <v>0</v>
+      <c r="T49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U49" s="3">
         <v>0</v>
@@ -3612,8 +3722,11 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3689,8 +3802,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3766,71 +3882,74 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>878600</v>
+      </c>
+      <c r="E52" s="3">
         <v>969600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>941200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>970100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>944700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>903100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>785000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>644200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>552500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>421100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>346500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>301900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>285200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>234600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>186500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>169700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>160000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>138400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>120100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>86400</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3843,8 +3962,11 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3920,71 +4042,74 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>11341000</v>
+      </c>
+      <c r="E54" s="3">
         <v>10785300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>9606800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8902200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8336900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7649700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6687800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5928500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5504200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5060400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4566100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3756600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3587600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3154300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2867600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2682200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2487100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2149800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1952700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1769500</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3997,8 +4122,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4026,8 +4154,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4055,71 +4184,72 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>355800</v>
+      </c>
+      <c r="E57" s="3">
         <v>194600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>138800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>123500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>116100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>94600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>82500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>72500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>55000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>53600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>40000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>33900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>39900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>29300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>27600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>59700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>36200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>40300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>45100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>34900</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4132,71 +4262,74 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>484800</v>
+      </c>
+      <c r="E58" s="3">
         <v>471300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>242900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>210100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>215200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>191900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>166600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>155800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>130500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>119300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>128900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>116300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>111000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>109700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>114100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>100700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>102500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>59400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>75900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>51500</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4209,71 +4342,74 @@
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>254700</v>
+      </c>
+      <c r="E59" s="3">
         <v>202900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>198700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>194400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>210600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>171600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>138700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>117400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>125400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>90300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>70200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>67100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>60000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>46500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>48000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>30500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>56300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>31400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>37600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>23700</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4286,71 +4422,74 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1095300</v>
+      </c>
+      <c r="E60" s="3">
         <v>868800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>580500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>528000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>541900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>458100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>387700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>345600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>310900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>263200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>239100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>217300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>210900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>185500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>189800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>190900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>195000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>131200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>158600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>110100</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4363,71 +4502,74 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7032400</v>
+      </c>
+      <c r="E61" s="3">
         <v>6712100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6125000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5622300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5195700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4808100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3986800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3462600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3136700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2933200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2593900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1994900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1924900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1795000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1628700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1511600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1346400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1116400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1152900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1016400</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -4440,71 +4582,74 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1084400</v>
+      </c>
+      <c r="E62" s="3">
         <v>1002500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>913200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>805200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>711800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>630200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>535600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>467600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>435000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>371800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>320600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>183400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>171200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>162400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>149200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>145300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>127400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>119100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>92000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>75600</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4517,8 +4662,11 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4594,8 +4742,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4671,8 +4822,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4748,71 +4902,74 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9814100</v>
+      </c>
+      <c r="E66" s="3">
         <v>9227400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>8217000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7623400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7063800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6403300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5387400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4694900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4314700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3965300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3499400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2733700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2635900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2431700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2205900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2090200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1841100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1523200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1511100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1296100</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4825,8 +4982,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4854,8 +5014,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4931,8 +5092,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5008,8 +5172,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5065,14 +5232,14 @@
         <v>0</v>
       </c>
       <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
         <v>600</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>1400</v>
       </c>
-      <c r="W70" s="3">
-        <v>0</v>
-      </c>
       <c r="X70" s="3">
         <v>0</v>
       </c>
@@ -5085,8 +5252,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5162,71 +5332,74 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-228600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-191500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-272200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-367000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-364800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-387100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-377200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-423500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-459700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-505800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-529900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-524500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-531000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-476100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-426500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-418600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-361800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-365400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-347200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-314700</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5239,8 +5412,11 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5316,8 +5492,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5393,8 +5572,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5470,71 +5652,74 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1526900</v>
+      </c>
+      <c r="E76" s="3">
         <v>1557900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1389800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1278800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1273100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1246400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1300400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1233600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1189500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1095200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1066700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1022900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>951700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>722600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>661700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>592000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>645900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>626600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>441000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>472000</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5547,8 +5732,11 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5624,167 +5812,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-187600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-63100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-86100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-81100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-29000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-64500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-41100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-35100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-14200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-27500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-63400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-33000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-91800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-64200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-25300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-71100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-17500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-37600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-63300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-50700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-53000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-17900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-23300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-41700</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5812,85 +6009,89 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>52500</v>
+      </c>
+      <c r="E83" s="3">
         <v>47200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>42300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>39800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>36900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>34700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>33200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>31900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>30600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>29000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>27800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>19500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>18300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>17000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>15900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>14900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>14400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>12300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>11600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>11000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>10400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>10600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>9400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>9000</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5966,8 +6167,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6043,8 +6247,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6120,8 +6327,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6197,8 +6407,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6274,85 +6487,91 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-42800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-12200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-13200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-169300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-67600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-103500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-70200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-92100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-62400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-36200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-60800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-49900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-29700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-18900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-24800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-58100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-95700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-18800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-31300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-24400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>13700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-4700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-19200</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6380,85 +6599,89 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-517500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-567000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-458900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-289300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-230700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-257100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-242300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-138200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-210500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-107700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-118900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-117500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-138500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-165500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-133100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-141200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-131600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-134400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-95900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-68900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-68400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-60200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-63100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-61000</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6534,8 +6757,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6611,85 +6837,91 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-652900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-717800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-649600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-524300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-530200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-557400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-536300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-357700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-394000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-338000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-283000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-226200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-235200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-236700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-173300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-184300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-178600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-172300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-124700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-92700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-89000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-88000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-87500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-84300</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6717,8 +6949,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6794,8 +7027,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6871,8 +7107,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6948,8 +7187,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7025,85 +7267,91 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>465000</v>
+      </c>
+      <c r="E100" s="3">
         <v>1049300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>647900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>568900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>603600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>836800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>645500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>382800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>328000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>425300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>549400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>161700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>431100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>282800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>213300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>261400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>315400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>200900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>176200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>109400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>62500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>110200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>47200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>145800</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7179,81 +7427,87 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-230700</v>
+      </c>
+      <c r="E102" s="3">
         <v>319200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-14900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-124800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>5700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>176000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>39000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-67000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-128400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>51200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>205600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-114400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>166200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>27300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>15200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>18900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>41000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>9800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>20200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-7800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-12900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>17500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-41700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>42300</v>
       </c>
-      <c r="AA102" s="3" t="s">
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NOVA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NOVA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="92">
   <si>
     <t>NOVA</t>
   </si>
@@ -656,365 +656,378 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>160900</v>
+      </c>
+      <c r="E8" s="3">
         <v>194200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>198400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>166400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>161700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>195600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>149400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>147000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>65700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>65000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>68900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>66600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>41300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>38000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>50200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>42800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>29800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>33600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>36600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>34600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>26700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>25200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>30400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>29000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>19800</v>
       </c>
-      <c r="AB8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>103400</v>
+      </c>
+      <c r="E9" s="3">
         <v>124600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>115400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>88300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>99200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>134300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>81100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>82100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>29500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>29100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>27000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>23500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>18600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>17700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>16500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>16900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>14000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>13700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>12100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>11300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>10300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>9800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>10000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>8700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>8300</v>
       </c>
-      <c r="AB9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>57500</v>
+      </c>
+      <c r="E10" s="3">
         <v>69600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>83000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>78100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>62500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>61300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>68300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>64900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>36200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>35900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>41900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>43100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>22700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>20300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>33700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>25900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>15800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>19900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>24500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>23300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>16400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>15400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>20400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>20300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>11500</v>
       </c>
-      <c r="AB10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1043,8 +1056,9 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1123,8 +1137,11 @@
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1203,88 +1220,94 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>13200</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>1200</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>9800</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
         <v>92100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>50700</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>10600</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>3</v>
+      <c r="AA14" s="3">
+        <v>0</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1363,8 +1386,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1390,168 +1416,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>245100</v>
+      </c>
+      <c r="E17" s="3">
         <v>290800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>236600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>226100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>210500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>212400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>177100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>149700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>99900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>74100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>77100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>90700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>64600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>148100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>99200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>47900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>44100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>42800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>42500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>48000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>31200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>37600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>27000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>26500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>26900</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-84200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-96600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-38200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-59700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-48800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-16800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-27700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-34200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-9100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-8200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-24100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-23300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-110100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-49000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-5100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-14300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-9200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-5900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-13400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-4500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-12400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>3400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-7100</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1580,349 +1613,362 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>35700</v>
+      </c>
+      <c r="E20" s="3">
         <v>34200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>30000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>23100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>24500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>22100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>16200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>13500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>12100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>9500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>8900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>8000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>7300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>8000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>5900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>6900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>4600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>3600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>3100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>2400</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>1800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1400</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-9900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>39000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>5700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>15600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>42200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>23200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>43900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>9800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>31000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>29700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>11700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-83800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-26200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>17700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>5300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>8800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>9600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>6500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>15800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>13300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1800</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>84600</v>
+      </c>
+      <c r="E22" s="3">
         <v>171800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>57600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>56900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>85600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>71500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>20800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>24600</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
         <v>31500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>26600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>50100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>8100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>26800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>30000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>30500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>67300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>8200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>31600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>38900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>31000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>26700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>11800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>13100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>6300</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-133100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-234200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-65800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-93600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-109800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-66200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-32300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-13800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-22100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-31100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-25900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-66300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-24100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-128800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-73100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-28700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-77000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-13800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-34400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-49800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-35500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-39100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-6600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-9200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-13400</v>
       </c>
-      <c r="AB23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-43000</v>
+      </c>
+      <c r="E24" s="3">
         <v>600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-9300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3900</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
         <v>0</v>
       </c>
@@ -1930,26 +1976,26 @@
         <v>0</v>
       </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>200</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
@@ -1980,8 +2026,11 @@
       <c r="AB24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2060,168 +2109,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-90100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-234800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-56500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-100800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-110300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-70100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-32300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-13800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-22100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-31300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-25900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-66300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-24100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-128800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-73300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-28700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-77000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-13800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-34400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-49800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-35500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-39100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-6600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-9200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-13400</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-70000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-187600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-63100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-86100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-81100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-29000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-64500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-41100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-35100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-14200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-27500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-63400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-33000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-91800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-64200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-25300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-71100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-17500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-37600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-63300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-50700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-53000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-17900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-23300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-41700</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2300,8 +2358,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2380,8 +2441,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2460,8 +2524,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2540,168 +2607,177 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-35700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-34200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-30000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-23100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-24500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-22100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-16200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-13500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-12100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-9500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-8900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-8000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-7300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-5900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-6900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-4600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-3600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-3100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-2400</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-70000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-187600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-63100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-86100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-81100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-29000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-64500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-41100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-35100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-14200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-27500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-63400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-33000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-91800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-64200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-25300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-71100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-17500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-37600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-63300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-50700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-53000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-17900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-23300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-41700</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2780,173 +2856,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-70000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-187600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-63100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-86100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-81100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-29000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-64500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-41100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-35100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-14200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-27500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-63400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-33000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-91800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-64200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-25300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-71100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-17500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-37600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-63300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-50700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-53000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-17900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-23300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-41700</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2975,8 +3060,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3005,74 +3091,75 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>231700</v>
+      </c>
+      <c r="E41" s="3">
         <v>212800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>467900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>187300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>210900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>360300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>412600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>208100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>208500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>243100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>408200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>368600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>150900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>209900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>84600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>102300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>73400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>83500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>51000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>58800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>43900</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3085,8 +3172,11 @@
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3165,74 +3255,77 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>391900</v>
+      </c>
+      <c r="E43" s="3">
         <v>478100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>315600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>301600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>355400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>358800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>289900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>227800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>145300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>139200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>95400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>78000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>63200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>56500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>46100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>37100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>35400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>31600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>29000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>26900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>20800</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3245,74 +3338,77 @@
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>130800</v>
+      </c>
+      <c r="E44" s="3">
         <v>148600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>137700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>179200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>182900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>152100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>186600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>150700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>150500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>128000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>134900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>128000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>107700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>102600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>111000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>120800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>115100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>43700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>17100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>16500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>15800</v>
       </c>
-      <c r="X44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3325,74 +3421,77 @@
       <c r="AB44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>63000</v>
+      </c>
+      <c r="E45" s="3">
         <v>96700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>72800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>78600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>78900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>77200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>48300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>84100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>58300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>105500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>79300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>65100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>55000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>87700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>67700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>26600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>56000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>115500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>29300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>6800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>5500</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3405,74 +3504,77 @@
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>817400</v>
+      </c>
+      <c r="E46" s="3">
         <v>936200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>993900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>746800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>828100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>948400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>937300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>670700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>562600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>615700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>717700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>639700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>376800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>456700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>309400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>286800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>280000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>274300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>126400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>109000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>86000</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3485,74 +3587,77 @@
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3890800</v>
+      </c>
+      <c r="E47" s="3">
         <v>3736000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3531100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>3228300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2864500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2466100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2072300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1736600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1450000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1204100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>962500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>773500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>622900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>513400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>428600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>379000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>338500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>298000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>255100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>223600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>197800</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3565,74 +3670,77 @@
       <c r="AB47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6059400</v>
+      </c>
+      <c r="E48" s="3">
         <v>5656100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5136400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4529100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4070900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3802000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3554800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3306100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3075200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2928300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2748300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2602300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2455000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2332300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2181700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2015300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1894000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1754700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1629900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1499900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1399300</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3645,47 +3753,50 @@
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>126500</v>
+      </c>
+      <c r="E49" s="3">
         <v>134100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>154300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>161400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>168600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>175700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>182300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>189400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>196600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>203700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>210900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>204200</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3701,8 +3812,8 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
+      <c r="U49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V49" s="3">
         <v>0</v>
@@ -3725,8 +3836,11 @@
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3805,8 +3919,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3885,74 +4002,77 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>921400</v>
+      </c>
+      <c r="E52" s="3">
         <v>878600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>969600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>941200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>970100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>944700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>903100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>785000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>644200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>552500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>421100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>346500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>301900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>285200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>234600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>186500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>169700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>160000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>138400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>120100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>86400</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3965,8 +4085,11 @@
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4045,74 +4168,77 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>11815600</v>
+      </c>
+      <c r="E54" s="3">
         <v>11341000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10785300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>9606800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8902200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8336900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7649700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6687800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5928500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5504200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5060400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4566100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3756600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3587600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3154300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2867600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2682200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2487100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2149800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1952700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1769500</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4125,8 +4251,11 @@
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4155,8 +4284,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4185,74 +4315,75 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>374900</v>
+      </c>
+      <c r="E57" s="3">
         <v>355800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>194600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>138800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>123500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>116100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>94600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>82500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>72500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>55000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>53600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>40000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>33900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>39900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>29300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>27600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>59700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>36200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>40300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>45100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>34900</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4265,74 +4396,77 @@
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>495000</v>
+      </c>
+      <c r="E58" s="3">
         <v>484800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>471300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>242900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>210100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>215200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>191900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>166600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>155800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>130500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>119300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>128900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>116300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>111000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>109700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>114100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>100700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>102500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>59400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>75900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>51500</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4345,74 +4479,77 @@
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>232600</v>
+      </c>
+      <c r="E59" s="3">
         <v>254700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>202900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>198700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>194400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>210600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>171600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>138700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>117400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>125400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>90300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>70200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>67100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>60000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>46500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>48000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>30500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>56300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>31400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>37600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>23700</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4425,74 +4562,77 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1102400</v>
+      </c>
+      <c r="E60" s="3">
         <v>1095300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>868800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>580500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>528000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>541900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>458100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>387700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>345600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>310900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>263200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>239100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>217300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>210900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>185500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>189800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>190900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>195000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>131200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>158600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>110100</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4505,74 +4645,77 @@
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7275500</v>
+      </c>
+      <c r="E61" s="3">
         <v>7032400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6712100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6125000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5622300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5195700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4808100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3986800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3462600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3136700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2933200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2593900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1994900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1924900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1795000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1628700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1511600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1346400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1116400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1152900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1016400</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -4585,74 +4728,77 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1115800</v>
+      </c>
+      <c r="E62" s="3">
         <v>1084400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1002500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>913200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>805200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>711800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>630200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>535600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>467600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>435000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>371800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>320600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>183400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>171200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>162400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>149200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>145300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>127400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>119100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>92000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>75600</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4665,8 +4811,11 @@
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4745,8 +4894,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4825,8 +4977,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4905,74 +5060,77 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10211600</v>
+      </c>
+      <c r="E66" s="3">
         <v>9814100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9227400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>8217000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7623400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7063800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6403300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5387400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4694900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4314700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3965300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3499400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2733700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2635900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2431700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2205900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2090200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1841100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1523200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1511100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1296100</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4985,8 +5143,11 @@
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5015,8 +5176,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5095,8 +5257,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5175,8 +5340,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5235,14 +5403,14 @@
         <v>0</v>
       </c>
       <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
         <v>600</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>1400</v>
       </c>
-      <c r="X70" s="3">
-        <v>0</v>
-      </c>
       <c r="Y70" s="3">
         <v>0</v>
       </c>
@@ -5255,8 +5423,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5335,74 +5506,77 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-163000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-228600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-191500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-272200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-367000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-364800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-387100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-377200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-423500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-459700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-505800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-529900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-524500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-531000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-476100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-426500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-418600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-361800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-365400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-347200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-314700</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5415,8 +5589,11 @@
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5495,8 +5672,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5575,8 +5755,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5655,74 +5838,77 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1604000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1526900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1557900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1389800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1278800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1273100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1246400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1300400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1233600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1189500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1095200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1066700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1022900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>951700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>722600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>661700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>592000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>645900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>626600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>441000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>472000</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5735,8 +5921,11 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5815,173 +6004,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-70000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-187600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-63100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-86100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-81100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-29000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-64500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-41100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-35100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-14200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-27500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-63400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-33000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-91800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-64200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-25300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-71100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-17500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-37600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-63300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-50700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-53000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-17900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-23300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-41700</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6010,88 +6208,92 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>57900</v>
+      </c>
+      <c r="E83" s="3">
         <v>52500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>47200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>42300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>39800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>36900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>34700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>33200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>31900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>30600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>29000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>27800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>19500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>18300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>17000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>15900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>14900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>14400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>12300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>11600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>11000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>10400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>10600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>9400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>9000</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6170,8 +6372,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6250,8 +6455,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6330,8 +6538,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6410,8 +6621,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6490,88 +6704,94 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-65600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-42800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-12200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-13200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-169300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-67600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-103500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-70200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-92100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-62400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-36200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-60800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-49900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-29700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-18900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-24800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-58100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-95700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-18800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-31300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-24400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>13700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-4700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-19200</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6600,88 +6820,92 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-398800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-517500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-567000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-458900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-289300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-230700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-257100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-242300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-138200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-210500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-107700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-118900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-117500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-138500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-165500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-133100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-141200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-131600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-134400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-95900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-68900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-68400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-60200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-63100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-61000</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6760,8 +6984,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6840,88 +7067,94 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-458700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-652900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-717800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-649600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-524300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-530200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-557400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-536300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-357700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-394000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-338000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-283000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-226200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-235200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-236700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-173300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-184300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-178600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-172300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-124700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-92700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-89000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-88000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-87500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-84300</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6950,8 +7183,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7030,8 +7264,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7110,8 +7347,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7190,8 +7430,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7270,88 +7513,94 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>517400</v>
+      </c>
+      <c r="E100" s="3">
         <v>465000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1049300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>647900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>568900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>603600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>836800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>645500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>382800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>328000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>425300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>549400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>161700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>431100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>282800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>213300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>261400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>315400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>200900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>176200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>109400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>62500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>110200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>47200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>145800</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7430,84 +7679,90 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-230700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>319200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-14900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-124800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>5700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>176000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>39000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-67000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-128400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>51200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>205600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-114400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>166200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>27300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>15200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>18900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>41000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>9800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>20200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-7800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-12900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>17500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-41700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>42300</v>
       </c>
-      <c r="AB102" s="3" t="s">
+      <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NOVA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NOVA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="92">
   <si>
     <t>NOVA</t>
   </si>
@@ -656,378 +656,391 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>219600</v>
+      </c>
+      <c r="E8" s="3">
         <v>160900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>194200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>198400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>166400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>161700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>195600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>149400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>147000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>65700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>65000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>68900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>66600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>41300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>38000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>50200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>42800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>29800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>33600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>36600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>34600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>26700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>25200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>30400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>29000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>19800</v>
       </c>
-      <c r="AC8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>113400</v>
+      </c>
+      <c r="E9" s="3">
         <v>103400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>124600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>115400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>88300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>99200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>134300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>81100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>82100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>29500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>29100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>27000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>23500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>18600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>17700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>16500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>16900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>14000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>13700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>12100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>11300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>10300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>9800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>10000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>8700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>8300</v>
       </c>
-      <c r="AC9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>106200</v>
+      </c>
+      <c r="E10" s="3">
         <v>57500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>69600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>83000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>78100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>62500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>61300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>68300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>64900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>36200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>35900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>41900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>43100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>22700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>20300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>33700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>25900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>15800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>19900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>24500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>23300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>16400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>15400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>20400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>20300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>11500</v>
       </c>
-      <c r="AC10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1057,8 +1070,9 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1140,8 +1154,11 @@
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1223,91 +1240,97 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>13200</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>1200</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>9800</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3">
         <v>92100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>50700</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>10600</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>3</v>
+      <c r="AB14" s="3">
+        <v>0</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1389,8 +1412,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1417,174 +1443,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>278500</v>
+      </c>
+      <c r="E17" s="3">
         <v>245100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>290800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>236600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>226100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>210500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>212400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>177100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>149700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>99900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>74100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>77100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>90700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>64600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>148100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>99200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>47900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>44100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>42800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>42500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>48000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>31200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>37600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>27000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>26500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>26900</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-58900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-84200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-96600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-38200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-59700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-48800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-16800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-27700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-34200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-9100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-8200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-24100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-23300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-110100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-49000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-5100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-14300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-9200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-5900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-13400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-12400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>3400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-7100</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1614,364 +1647,377 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>30500</v>
+      </c>
+      <c r="E20" s="3">
         <v>35700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>34200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>30000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>23100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>24500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>22100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>16200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>13500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>12100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>9500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>8900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>8000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>7300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>8000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>5900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>6900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>4600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>3600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>3100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2400</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
         <v>0</v>
       </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>1800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1400</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>34500</v>
+      </c>
+      <c r="E21" s="3">
         <v>9400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-9900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>39000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>5700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>15600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>42200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>23200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>43900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>9800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>31000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>29700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>11700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-83800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-26200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>17700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>5300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>8800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>9600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>6500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>15800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>13300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1800</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>121500</v>
+      </c>
+      <c r="E22" s="3">
         <v>84600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>171800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>57600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>56900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>85600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>71500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>20800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>24600</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
         <v>31500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>26600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>50100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>8100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>26800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>30000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>30500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>67300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>8200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>31600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>38900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>31000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>26700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>11800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>13100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>6300</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-150000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-133100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-234200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-65800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-93600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-109800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-66200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-32300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-13800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-22100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-31100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-25900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-66300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-24100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-128800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-73100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-28700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-77000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-13800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-34400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-49800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-35500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-39100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-6600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-9200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-13400</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-70300</v>
+      </c>
+      <c r="E24" s="3">
         <v>-43000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-9300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>7200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3900</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
         <v>0</v>
       </c>
@@ -1979,26 +2025,26 @@
         <v>0</v>
       </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>200</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
         <v>0</v>
       </c>
@@ -2029,8 +2075,11 @@
       <c r="AC24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2112,174 +2161,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-79700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-90100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-234800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-56500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-100800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-110300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-70100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-32300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-13800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-22100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-31300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-25900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-66300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-24100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-128800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-73300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-28700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-77000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-13800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-34400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-49800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-35500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-39100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-6600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-9200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-13400</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-33100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-70000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-187600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-63100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-86100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-81100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-29000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-64500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-41100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-35100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-14200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-27500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-63400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-33000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-91800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-64200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-25300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-71100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-17500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-37600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-63300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-50700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-53000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-17900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-23300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-41700</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2361,8 +2419,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2444,8 +2505,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2527,8 +2591,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2610,174 +2677,183 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-30500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-35700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-34200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-30000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-23100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-24500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-22100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-16200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-13500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-12100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-9500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-8900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-8000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-7300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-8000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-5900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-6900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-4600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-3600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-3100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2400</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
         <v>0</v>
       </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-33100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-70000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-187600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-63100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-86100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-81100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-29000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-64500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-41100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-35100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-14200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-27500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-63400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-33000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-91800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-64200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-25300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-71100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-17500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-37600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-63300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-50700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-53000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-17900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-23300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-41700</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2859,179 +2935,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-33100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-70000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-187600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-63100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-86100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-81100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-29000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-64500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-41100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-35100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-14200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-27500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-63400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-33000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-91800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-64200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-25300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-71100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-17500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-37600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-63300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-50700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-53000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-17900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-23300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-41700</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3061,8 +3146,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3092,77 +3178,78 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>253200</v>
+      </c>
+      <c r="E41" s="3">
         <v>231700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>212800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>467900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>187300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>210900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>360300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>412600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>208100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>208500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>243100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>408200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>368600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>150900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>209900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>84600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>102300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>73400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>83500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>51000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>58800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>43900</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3175,8 +3262,11 @@
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3258,77 +3348,80 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>531700</v>
+      </c>
+      <c r="E43" s="3">
         <v>391900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>478100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>315600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>301600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>355400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>358800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>289900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>227800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>145300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>139200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>95400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>78000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>63200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>56500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>46100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>37100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>35400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>31600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>29000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>26900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>20800</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3341,77 +3434,80 @@
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>132100</v>
+      </c>
+      <c r="E44" s="3">
         <v>130800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>148600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>137700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>179200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>182900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>152100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>186600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>150700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>150500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>128000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>134900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>128000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>107700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>102600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>111000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>120800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>115100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>43700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>17100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>16500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>15800</v>
       </c>
-      <c r="Y44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3424,77 +3520,80 @@
       <c r="AC44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>136200</v>
+      </c>
+      <c r="E45" s="3">
         <v>63000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>96700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>72800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>78600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>78900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>77200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>48300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>84100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>58300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>105500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>79300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>65100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>55000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>87700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>67700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>26600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>56000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>115500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>29300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>6800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>5500</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3507,77 +3606,80 @@
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1053200</v>
+      </c>
+      <c r="E46" s="3">
         <v>817400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>936200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>993900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>746800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>828100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>948400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>937300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>670700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>562600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>615700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>717700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>639700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>376800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>456700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>309400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>286800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>280000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>274300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>126400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>109000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>86000</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3590,77 +3692,80 @@
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3884900</v>
+      </c>
+      <c r="E47" s="3">
         <v>3890800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3736000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>3531100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>3228300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2864500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2466100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2072300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1736600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1450000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1204100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>962500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>773500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>622900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>513400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>428600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>379000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>338500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>298000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>255100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>223600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>197800</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3673,77 +3778,80 @@
       <c r="AC47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6496100</v>
+      </c>
+      <c r="E48" s="3">
         <v>6059400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5656100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5136400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4529100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4070900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3802000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3554800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3306100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3075200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2928300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2748300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2602300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2455000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2332300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2181700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2015300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1894000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1754700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1629900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1499900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1399300</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3756,50 +3864,53 @@
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>119400</v>
+      </c>
+      <c r="E49" s="3">
         <v>126500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>134100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>154300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>161400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>168600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>175700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>182300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>189400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>196600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>203700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>210900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>204200</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3815,8 +3926,8 @@
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V49" s="3">
-        <v>0</v>
+      <c r="V49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W49" s="3">
         <v>0</v>
@@ -3839,8 +3950,11 @@
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3922,8 +4036,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4005,77 +4122,80 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1007100</v>
+      </c>
+      <c r="E52" s="3">
         <v>921400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>878600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>969600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>941200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>970100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>944700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>903100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>785000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>644200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>552500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>421100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>346500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>301900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>285200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>234600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>186500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>169700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>160000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>138400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>120100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>86400</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4088,8 +4208,11 @@
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4171,77 +4294,80 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>12560700</v>
+      </c>
+      <c r="E54" s="3">
         <v>11815600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>11341000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10785300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>9606800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8902200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8336900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7649700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6687800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5928500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5504200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5060400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4566100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3756600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3587600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3154300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2867600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2682200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2487100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2149800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1952700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1769500</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4254,8 +4380,11 @@
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4285,8 +4414,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4316,77 +4446,78 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>504100</v>
+      </c>
+      <c r="E57" s="3">
         <v>374900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>355800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>194600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>138800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>123500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>116100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>94600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>82500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>72500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>55000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>53600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>40000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>33900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>39900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>29300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>27600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>59700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>36200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>40300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>45100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>34900</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4399,77 +4530,80 @@
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>334700</v>
+      </c>
+      <c r="E58" s="3">
         <v>495000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>484800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>471300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>242900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>210100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>215200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>191900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>166600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>155800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>130500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>119300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>128900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>116300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>111000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>109700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>114100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>100700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>102500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>59400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>75900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>51500</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4482,77 +4616,80 @@
       <c r="AC58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>248800</v>
+      </c>
+      <c r="E59" s="3">
         <v>232600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>254700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>202900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>198700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>194400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>210600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>171600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>138700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>117400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>125400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>90300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>70200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>67100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>60000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>46500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>48000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>30500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>56300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>31400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>37600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>23700</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4565,77 +4702,80 @@
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1087600</v>
+      </c>
+      <c r="E60" s="3">
         <v>1102400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1095300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>868800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>580500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>528000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>541900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>458100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>387700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>345600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>310900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>263200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>239100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>217300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>210900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>185500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>189800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>190900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>195000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>131200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>158600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>110100</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4648,77 +4788,80 @@
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7646500</v>
+      </c>
+      <c r="E61" s="3">
         <v>7275500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7032400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6712100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6125000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5622300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5195700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4808100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3986800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3462600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3136700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2933200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2593900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1994900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1924900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1795000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1628700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1511600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1346400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1116400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1152900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1016400</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
@@ -4731,77 +4874,80 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1152000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1115800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1084400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1002500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>913200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>805200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>711800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>630200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>535600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>467600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>435000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>371800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>320600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>183400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>171200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>162400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>149200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>145300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>127400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>119100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>92000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>75600</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4814,8 +4960,11 @@
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4897,8 +5046,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4980,8 +5132,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5063,77 +5218,80 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10817600</v>
+      </c>
+      <c r="E66" s="3">
         <v>10211600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9814100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9227400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>8217000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7623400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7063800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6403300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5387400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4694900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4314700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3965300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3499400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2733700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2635900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2431700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2205900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2090200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1841100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1523200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1511100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1296100</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5146,8 +5304,11 @@
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5177,8 +5338,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5260,8 +5422,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5343,8 +5508,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5406,14 +5574,14 @@
         <v>0</v>
       </c>
       <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
         <v>600</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>1400</v>
       </c>
-      <c r="Y70" s="3">
-        <v>0</v>
-      </c>
       <c r="Z70" s="3">
         <v>0</v>
       </c>
@@ -5426,8 +5594,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5509,77 +5680,80 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-32400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-163000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-228600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-191500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-272200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-367000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-364800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-387100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-377200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-423500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-459700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-505800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-529900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-524500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-531000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-476100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-426500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-418600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-361800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-365400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-347200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-314700</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5592,8 +5766,11 @@
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5675,8 +5852,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5758,8 +5938,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5841,77 +6024,80 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1743100</v>
+      </c>
+      <c r="E76" s="3">
         <v>1604000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1526900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1557900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1389800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1278800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1273100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1246400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1300400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1233600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1189500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1095200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1066700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1022900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>951700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>722600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>661700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>592000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>645900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>626600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>441000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>472000</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5924,8 +6110,11 @@
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6007,179 +6196,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-33100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-70000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-187600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-63100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-86100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-81100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-29000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-64500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-41100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-35100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-14200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-27500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-63400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-33000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-91800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-64200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-25300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-71100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-17500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-37600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-63300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-50700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-53000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-17900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-23300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-41700</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6209,91 +6407,95 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>62900</v>
+      </c>
+      <c r="E83" s="3">
         <v>57900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>52500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>47200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>42300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>39800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>36900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>34700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>33200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>31900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>30600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>29000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>27800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>19500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>18300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>17000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>15900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>14900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>14400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>12300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>11600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>11000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>10400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>10600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>9400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>9000</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6375,8 +6577,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6458,8 +6663,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6541,8 +6749,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6624,8 +6835,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6707,91 +6921,97 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-80100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-65600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-42800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-12200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-13200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-169300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-67600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-103500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-70200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-92100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-62400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-36200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-60800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-49900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-29700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-18900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-24800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-58100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-95700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-18800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-31300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-24400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>13700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-4700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-19200</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6821,91 +7041,95 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-465700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-398800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-517500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-567000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-458900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-289300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-230700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-257100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-242300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-138200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-210500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-107700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-118900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-117500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-138500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-165500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-133100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-141200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-131600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-134400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-95900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-68900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-68400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-60200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-63100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-61000</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6987,8 +7211,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7070,91 +7297,97 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-424800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-458700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-652900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-717800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-649600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-524300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-530200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-557400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-536300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-357700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-394000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-338000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-283000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-226200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-235200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-236700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-173300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-184300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-178600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-172300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-124700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-92700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-89000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-88000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-87500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-84300</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7184,8 +7417,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7267,8 +7501,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7350,8 +7587,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7433,8 +7673,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7516,91 +7759,97 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>647800</v>
+      </c>
+      <c r="E100" s="3">
         <v>517400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>465000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1049300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>647900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>568900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>603600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>836800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>645500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>382800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>328000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>425300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>549400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>161700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>431100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>282800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>213300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>261400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>315400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>200900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>176200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>109400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>62500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>110200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>47200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>145800</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7682,87 +7931,93 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>142900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-6900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-230700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>319200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-14900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-124800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>5700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>176000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>39000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-67000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-128400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>51200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>205600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-114400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>166200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>27300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>15200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>18900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>41000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>9800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>20200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-7800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-12900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>17500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-41700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>42300</v>
       </c>
-      <c r="AC102" s="3" t="s">
+      <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NOVA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NOVA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="92">
   <si>
     <t>NOVA</t>
   </si>
@@ -656,391 +656,404 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>235300</v>
+      </c>
+      <c r="E8" s="3">
         <v>219600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>160900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>194200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>198400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>166400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>161700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>195600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>149400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>147000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>65700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>65000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>68900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>66600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>41300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>38000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>50200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>42800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>29800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>33600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>36600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>34600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>26700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>25200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>30400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>29000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>19800</v>
       </c>
-      <c r="AD8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>113400</v>
+        <v>157300</v>
       </c>
       <c r="E9" s="3">
-        <v>103400</v>
+        <v>83900</v>
       </c>
       <c r="F9" s="3">
-        <v>124600</v>
+        <v>76500</v>
       </c>
       <c r="G9" s="3">
-        <v>115400</v>
+        <v>97200</v>
       </c>
       <c r="H9" s="3">
-        <v>88300</v>
+        <v>134100</v>
       </c>
       <c r="I9" s="3">
-        <v>99200</v>
+        <v>87800</v>
       </c>
       <c r="J9" s="3">
+        <v>81100</v>
+      </c>
+      <c r="K9" s="3">
         <v>134300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>81100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>82100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>29500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>29100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>27000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>23500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>18600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>17700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>16500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>16900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>14000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>13700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>12100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>11300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>10300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>9800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>10000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>8700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>8300</v>
       </c>
-      <c r="AD9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>106200</v>
+        <v>78000</v>
       </c>
       <c r="E10" s="3">
-        <v>57500</v>
+        <v>135700</v>
       </c>
       <c r="F10" s="3">
-        <v>69600</v>
+        <v>84400</v>
       </c>
       <c r="G10" s="3">
-        <v>83000</v>
+        <v>97000</v>
       </c>
       <c r="H10" s="3">
-        <v>78100</v>
+        <v>64300</v>
       </c>
       <c r="I10" s="3">
-        <v>62500</v>
+        <v>78600</v>
       </c>
       <c r="J10" s="3">
+        <v>80600</v>
+      </c>
+      <c r="K10" s="3">
         <v>61300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>68300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>64900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>36200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>35900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>41900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>43100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>22700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>20300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>33700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>25900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>15800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>19900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>24500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>23300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>16400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>15400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>20400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>20300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>11500</v>
       </c>
-      <c r="AD10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1071,8 +1084,9 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1157,8 +1171,11 @@
       <c r="AD12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1243,8 +1260,11 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1255,10 +1275,10 @@
         <v>3</v>
       </c>
       <c r="F14" s="3">
-        <v>13200</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
+        <v>9400</v>
+      </c>
+      <c r="G14" s="3">
+        <v>39800</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -1267,93 +1287,96 @@
         <v>3</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>1200</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>9800</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S14" s="3">
         <v>92100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>50700</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>10600</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>3</v>
+      <c r="AC14" s="3">
+        <v>0</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>68400</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>46400</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>42200</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>38000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>48400</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>30300</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>28200</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1415,8 +1438,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1444,180 +1470,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>287800</v>
+      </c>
+      <c r="E17" s="3">
         <v>278500</v>
       </c>
-      <c r="E17" s="3">
-        <v>245100</v>
-      </c>
       <c r="F17" s="3">
-        <v>290800</v>
+        <v>235700</v>
       </c>
       <c r="G17" s="3">
+        <v>254200</v>
+      </c>
+      <c r="H17" s="3">
         <v>236600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>226100</v>
       </c>
-      <c r="I17" s="3">
-        <v>210500</v>
-      </c>
       <c r="J17" s="3">
+        <v>210600</v>
+      </c>
+      <c r="K17" s="3">
         <v>212400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>177100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>149700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>99900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>74100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>77100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>90700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>64600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>148100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>99200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>47900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>44100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>42800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>42500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>48000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>31200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>37600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>27000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>26500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>26900</v>
       </c>
-      <c r="AD17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-52500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-58900</v>
       </c>
-      <c r="E18" s="3">
-        <v>-84200</v>
-      </c>
       <c r="F18" s="3">
-        <v>-96600</v>
+        <v>-74800</v>
       </c>
       <c r="G18" s="3">
+        <v>-60000</v>
+      </c>
+      <c r="H18" s="3">
         <v>-38200</v>
       </c>
-      <c r="H18" s="3">
-        <v>-59700</v>
-      </c>
       <c r="I18" s="3">
-        <v>-48800</v>
+        <v>-59800</v>
       </c>
       <c r="J18" s="3">
+        <v>-48900</v>
+      </c>
+      <c r="K18" s="3">
         <v>-16800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-27700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-34200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-9100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-8200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-24100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-23300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-110100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-49000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-5100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-14300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-9200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-5900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-13400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-4500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-12400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>3400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-7100</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1648,379 +1681,392 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>30500</v>
+      <c r="D20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E20" s="3">
-        <v>35700</v>
+        <v>4900</v>
       </c>
       <c r="F20" s="3">
-        <v>34200</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>30000</v>
+        <v>-3100</v>
       </c>
       <c r="H20" s="3">
-        <v>23100</v>
+        <v>600</v>
       </c>
       <c r="I20" s="3">
-        <v>24500</v>
+        <v>3200</v>
       </c>
       <c r="J20" s="3">
+        <v>200</v>
+      </c>
+      <c r="K20" s="3">
         <v>22100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>16200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>13500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>12100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>9500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>8900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>8000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>7300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>8000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>5900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>6900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>4600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>3600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>3100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>2400</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
         <v>0</v>
       </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>1800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1400</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>34500</v>
+        <v>15900</v>
       </c>
       <c r="E21" s="3">
-        <v>9400</v>
+        <v>-17400</v>
       </c>
       <c r="F21" s="3">
-        <v>-9900</v>
+        <v>-32600</v>
       </c>
       <c r="G21" s="3">
-        <v>39000</v>
+        <v>-18900</v>
       </c>
       <c r="H21" s="3">
-        <v>5700</v>
+        <v>9700</v>
       </c>
       <c r="I21" s="3">
-        <v>15600</v>
+        <v>-32600</v>
       </c>
       <c r="J21" s="3">
+        <v>-20900</v>
+      </c>
+      <c r="K21" s="3">
         <v>42200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>23200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>43900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>9800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>31000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>29700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>11700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-83800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-26200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>17700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>5300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>8800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>9600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>6500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>15800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>13300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1800</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>182500</v>
+      </c>
+      <c r="E22" s="3">
         <v>121500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>84600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>171800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>57600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>56900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>85600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>71500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>20800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>24600</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
       <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
         <v>31500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>26600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>50100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>8100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>26800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>30000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>30500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>67300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>8200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>31600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>38900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>31000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>26700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>11800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>13100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>6300</v>
       </c>
-      <c r="AD22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-196500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-150000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-133100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-234200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-65800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-93600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-109800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-66200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-32300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-13800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-22100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-31100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-25900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-66300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-24100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-128800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-73100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-28700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-77000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-13800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-34400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-49800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-35500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-39100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-6600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-9200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-13400</v>
       </c>
-      <c r="AD23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-46100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-70300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-43000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-9300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>7200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3900</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
         <v>0</v>
       </c>
@@ -2028,26 +2074,26 @@
         <v>0</v>
       </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
+      <c r="R24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>200</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
         <v>0</v>
       </c>
@@ -2078,8 +2124,11 @@
       <c r="AD24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2164,180 +2213,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-150300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-79700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-90100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-234800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-56500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-100800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-110300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-70100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-32300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-13800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-22100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-31300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-25900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-66300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-24100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-128800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-73300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-28700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-77000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-13800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-34400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-49800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-35500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-39100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-6600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-9200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-13400</v>
       </c>
-      <c r="AD26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-122600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-33100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-70000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-187600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-63100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-86100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-81100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-29000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-64500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-41100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-35100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-14200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-27500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-63400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-33000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-91800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-64200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-25300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-71100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-17500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-37600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-63300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-50700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-53000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-17900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-23300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-41700</v>
       </c>
-      <c r="AD27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2422,8 +2480,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2508,8 +2569,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2594,8 +2658,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2680,180 +2747,189 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-30500</v>
+      <c r="D32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E32" s="3">
-        <v>-35700</v>
+        <v>-4900</v>
       </c>
       <c r="F32" s="3">
-        <v>-34200</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>-30000</v>
+        <v>3100</v>
       </c>
       <c r="H32" s="3">
-        <v>-23100</v>
+        <v>-600</v>
       </c>
       <c r="I32" s="3">
-        <v>-24500</v>
+        <v>-3200</v>
       </c>
       <c r="J32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K32" s="3">
         <v>-22100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-16200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-13500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-12100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-9500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-8900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-7300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-8000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-5900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-6900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-4600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-3600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-3100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
         <v>0</v>
       </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-122600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-33100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-70000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-187600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-63100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-86100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-81100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-29000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-64500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-41100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-35100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-14200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-27500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-63400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-33000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-91800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-64200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-25300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-71100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-17500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-37600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-63300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-50700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-53000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-17900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-23300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-41700</v>
       </c>
-      <c r="AD33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2938,185 +3014,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-122600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-33100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-70000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-187600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-63100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-86100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-81100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-29000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-64500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-41100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-35100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-14200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-27500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-63400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-33000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-91800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-64200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-25300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-71100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-17500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-37600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-63300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-50700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-53000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-17900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-23300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-41700</v>
       </c>
-      <c r="AD35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3147,8 +3232,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3179,80 +3265,81 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>208900</v>
+      </c>
+      <c r="E41" s="3">
         <v>253200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>231700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>212800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>467900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>187300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>210900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>360300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>412600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>208100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>208500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>243100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>408200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>368600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>150900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>209900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>84600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>102300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>73400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>83500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>51000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>58800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>43900</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3265,31 +3352,34 @@
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>7400</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>7300</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>7600</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>7800</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -3351,80 +3441,83 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>531700</v>
+        <v>512500</v>
       </c>
       <c r="E43" s="3">
-        <v>391900</v>
+        <v>535100</v>
       </c>
       <c r="F43" s="3">
-        <v>478100</v>
+        <v>390100</v>
       </c>
       <c r="G43" s="3">
-        <v>315600</v>
+        <v>478300</v>
       </c>
       <c r="H43" s="3">
-        <v>301600</v>
+        <v>320900</v>
       </c>
       <c r="I43" s="3">
-        <v>355400</v>
+        <v>304200</v>
       </c>
       <c r="J43" s="3">
+        <v>353100</v>
+      </c>
+      <c r="K43" s="3">
         <v>358800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>289900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>227800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>145300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>139200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>95400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>78000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>63200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>56500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>46100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>37100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>35400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>31600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>29000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>26900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>20800</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3437,80 +3530,83 @@
       <c r="AD43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>136600</v>
+      </c>
+      <c r="E44" s="3">
         <v>132100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>130800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>148600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>137700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>179200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>182900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>152100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>186600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>150700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>150500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>128000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>134900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>128000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>107700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>102600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>111000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>120800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>115100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>43700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>17100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>16500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>15800</v>
       </c>
-      <c r="Z44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3523,80 +3619,83 @@
       <c r="AD44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>136200</v>
+        <v>100</v>
       </c>
       <c r="E45" s="3">
-        <v>63000</v>
+        <v>2900</v>
       </c>
       <c r="F45" s="3">
-        <v>96700</v>
+        <v>800</v>
       </c>
       <c r="G45" s="3">
-        <v>72800</v>
+        <v>900</v>
       </c>
       <c r="H45" s="3">
-        <v>78600</v>
+        <v>700</v>
       </c>
       <c r="I45" s="3">
-        <v>78900</v>
+        <v>700</v>
       </c>
       <c r="J45" s="3">
+        <v>100</v>
+      </c>
+      <c r="K45" s="3">
         <v>77200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>48300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>84100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>58300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>105500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>79300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>65100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>55000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>87700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>67700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>26600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>56000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>115500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>29300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>6800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>5500</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3609,80 +3708,83 @@
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>914600</v>
+      </c>
+      <c r="E46" s="3">
         <v>1053200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>817400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>936200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>993900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>746800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>828100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>948400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>937300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>670700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>562600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>615700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>717700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>639700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>376800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>456700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>309400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>286800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>280000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>274300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>126400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>109000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>86000</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3695,80 +3797,83 @@
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>3884900</v>
+        <v>63300</v>
       </c>
       <c r="E47" s="3">
-        <v>3890800</v>
+        <v>86800</v>
       </c>
       <c r="F47" s="3">
-        <v>3736000</v>
+        <v>114800</v>
       </c>
       <c r="G47" s="3">
-        <v>3531100</v>
+        <v>117300</v>
       </c>
       <c r="H47" s="3">
-        <v>3228300</v>
+        <v>186300</v>
       </c>
       <c r="I47" s="3">
-        <v>2864500</v>
+        <v>182800</v>
       </c>
       <c r="J47" s="3">
+        <v>196600</v>
+      </c>
+      <c r="K47" s="3">
         <v>2466100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2072300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1736600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1450000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1204100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>962500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>773500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>622900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>513400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>428600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>379000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>338500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>298000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>255100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>223600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>197800</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3781,80 +3886,83 @@
       <c r="AD47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>6496100</v>
+        <v>6884100</v>
       </c>
       <c r="E48" s="3">
-        <v>6059400</v>
+        <v>6405800</v>
       </c>
       <c r="F48" s="3">
-        <v>5656100</v>
+        <v>5974800</v>
       </c>
       <c r="G48" s="3">
-        <v>5136400</v>
+        <v>5577600</v>
       </c>
       <c r="H48" s="3">
-        <v>4529100</v>
+        <v>5065200</v>
       </c>
       <c r="I48" s="3">
-        <v>4070900</v>
+        <v>4464400</v>
       </c>
       <c r="J48" s="3">
+        <v>4010500</v>
+      </c>
+      <c r="K48" s="3">
         <v>3802000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3554800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3306100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3075200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2928300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2748300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2602300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2455000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2332300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2181700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2015300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1894000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1754700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1629900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1499900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1399300</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3867,53 +3975,56 @@
       <c r="AD48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>112300</v>
+      </c>
+      <c r="E49" s="3">
         <v>119400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>126500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>134100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>154300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>161400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>168600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>175700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>182300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>189400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>196600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>203700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>210900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>204200</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3929,8 +4040,8 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W49" s="3">
-        <v>0</v>
+      <c r="W49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X49" s="3">
         <v>0</v>
@@ -3953,8 +4064,11 @@
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4039,8 +4153,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4125,80 +4242,83 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1007100</v>
+        <v>775200</v>
       </c>
       <c r="E52" s="3">
-        <v>921400</v>
+        <v>847000</v>
       </c>
       <c r="F52" s="3">
-        <v>878600</v>
+        <v>701000</v>
       </c>
       <c r="G52" s="3">
-        <v>969600</v>
+        <v>617700</v>
       </c>
       <c r="H52" s="3">
-        <v>941200</v>
+        <v>604400</v>
       </c>
       <c r="I52" s="3">
-        <v>970100</v>
+        <v>517600</v>
       </c>
       <c r="J52" s="3">
+        <v>451600</v>
+      </c>
+      <c r="K52" s="3">
         <v>944700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>903100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>785000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>644200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>552500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>421100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>346500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>301900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>285200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>234600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>186500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>169700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>160000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>138400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>120100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>86400</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4211,8 +4331,11 @@
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4297,80 +4420,83 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>12882300</v>
+      </c>
+      <c r="E54" s="3">
         <v>12560700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>11815600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>11341000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10785300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>9606800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8902200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8336900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7649700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6687800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5928500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5504200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5060400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4566100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3756600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3587600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3154300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2867600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2682200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2487100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2149800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1952700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1769500</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4383,8 +4509,11 @@
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4415,8 +4544,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4447,80 +4577,81 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>484300</v>
+      </c>
+      <c r="E57" s="3">
         <v>504100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>374900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>355800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>194600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>138800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>123500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>116100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>94600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>82500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>72500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>55000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>53600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>40000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>33900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>39900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>29300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>27600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>59700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>36200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>40300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>45100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>34900</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4533,80 +4664,83 @@
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>334700</v>
+        <v>330100</v>
       </c>
       <c r="E58" s="3">
-        <v>495000</v>
+        <v>337700</v>
       </c>
       <c r="F58" s="3">
-        <v>484800</v>
+        <v>498000</v>
       </c>
       <c r="G58" s="3">
-        <v>471300</v>
+        <v>487700</v>
       </c>
       <c r="H58" s="3">
-        <v>242900</v>
+        <v>474100</v>
       </c>
       <c r="I58" s="3">
-        <v>210100</v>
+        <v>245400</v>
       </c>
       <c r="J58" s="3">
+        <v>212600</v>
+      </c>
+      <c r="K58" s="3">
         <v>215200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>191900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>166600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>155800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>130500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>119300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>128900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>116300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>111000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>109700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>114100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>100700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>102500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>59400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>75900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>51500</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4619,80 +4753,83 @@
       <c r="AD58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>248800</v>
+        <v>69800</v>
       </c>
       <c r="E59" s="3">
-        <v>232600</v>
+        <v>72500</v>
       </c>
       <c r="F59" s="3">
-        <v>254700</v>
+        <v>76000</v>
       </c>
       <c r="G59" s="3">
-        <v>202900</v>
+        <v>61800</v>
       </c>
       <c r="H59" s="3">
-        <v>198700</v>
+        <v>56900</v>
       </c>
       <c r="I59" s="3">
-        <v>194400</v>
+        <v>47700</v>
       </c>
       <c r="J59" s="3">
+        <v>43400</v>
+      </c>
+      <c r="K59" s="3">
         <v>210600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>171600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>138700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>117400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>125400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>90300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>70200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>67100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>60000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>46500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>48000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>30500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>56300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>31400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>37600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>23700</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4705,80 +4842,83 @@
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1059000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1087600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1102400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1095300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>868800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>580500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>528000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>541900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>458100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>387700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>345600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>310900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>263200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>239100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>217300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>210900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>185500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>189800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>190900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>195000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>131200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>158600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>110100</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4791,80 +4931,83 @@
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>7646500</v>
+        <v>7968800</v>
       </c>
       <c r="E61" s="3">
-        <v>7275500</v>
+        <v>7659000</v>
       </c>
       <c r="F61" s="3">
-        <v>7032400</v>
+        <v>7288800</v>
       </c>
       <c r="G61" s="3">
-        <v>6712100</v>
+        <v>7046400</v>
       </c>
       <c r="H61" s="3">
-        <v>6125000</v>
+        <v>6726500</v>
       </c>
       <c r="I61" s="3">
-        <v>5622300</v>
+        <v>6139800</v>
       </c>
       <c r="J61" s="3">
+        <v>5637400</v>
+      </c>
+      <c r="K61" s="3">
         <v>5195700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4808100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3986800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3462600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3136700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2933200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2593900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1994900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1924900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1795000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1628700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1511600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1346400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1116400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1152900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1016400</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
@@ -4877,80 +5020,83 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1152000</v>
+        <v>141800</v>
       </c>
       <c r="E62" s="3">
-        <v>1115800</v>
+        <v>128900</v>
       </c>
       <c r="F62" s="3">
-        <v>1084400</v>
+        <v>121200</v>
       </c>
       <c r="G62" s="3">
-        <v>1002500</v>
+        <v>130200</v>
       </c>
       <c r="H62" s="3">
-        <v>913200</v>
+        <v>124000</v>
       </c>
       <c r="I62" s="3">
-        <v>805200</v>
+        <v>121200</v>
       </c>
       <c r="J62" s="3">
+        <v>104300</v>
+      </c>
+      <c r="K62" s="3">
         <v>711800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>630200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>535600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>467600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>435000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>371800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>320600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>183400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>171200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>162400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>149200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>145300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>127400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>119100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>92000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>75600</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4963,8 +5109,11 @@
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5049,8 +5198,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5135,8 +5287,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5221,80 +5376,83 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>10817600</v>
+        <v>10198900</v>
       </c>
       <c r="E66" s="3">
-        <v>10211600</v>
+        <v>9886000</v>
       </c>
       <c r="F66" s="3">
-        <v>9814100</v>
+        <v>9493800</v>
       </c>
       <c r="G66" s="3">
-        <v>9227400</v>
+        <v>9212100</v>
       </c>
       <c r="H66" s="3">
-        <v>8217000</v>
+        <v>8583400</v>
       </c>
       <c r="I66" s="3">
-        <v>7623400</v>
+        <v>7618700</v>
       </c>
       <c r="J66" s="3">
+        <v>6955400</v>
+      </c>
+      <c r="K66" s="3">
         <v>7063800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6403300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5387400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4694900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4314700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3965300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3499400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2733700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2635900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2431700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2205900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2090200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1841100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1523200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1511100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1296100</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5307,8 +5465,11 @@
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5339,8 +5500,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5425,8 +5587,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5511,8 +5676,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5577,14 +5745,14 @@
         <v>0</v>
       </c>
       <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
         <v>600</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="Z70" s="3">
         <v>1400</v>
       </c>
-      <c r="Z70" s="3">
-        <v>0</v>
-      </c>
       <c r="AA70" s="3">
         <v>0</v>
       </c>
@@ -5597,8 +5765,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5683,80 +5854,83 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-32400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-163000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-228600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-191500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-272200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-367000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-364800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-387100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-377200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-423500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-459700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-505800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-529900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-524500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-531000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-476100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-426500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-418600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-361800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-365400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-347200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-314700</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5769,8 +5943,11 @@
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5855,8 +6032,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5941,8 +6121,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6027,80 +6210,83 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1778900</v>
+      </c>
+      <c r="E76" s="3">
         <v>1743100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1604000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1526900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1557900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1389800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1278800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1273100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1246400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1300400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1233600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1189500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1095200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1066700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1022900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>951700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>722600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>661700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>592000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>645900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>626600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>441000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>472000</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6113,8 +6299,11 @@
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6199,185 +6388,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-122600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-33100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-70000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-187600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-63100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-86100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-81100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-29000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-64500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-41100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-35100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-14200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-27500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-63400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-33000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-91800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-64200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-25300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-71100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-17500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-37600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-63300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-50700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-53000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-17900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-23300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-41700</v>
       </c>
-      <c r="AD81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6408,94 +6606,98 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>62900</v>
+        <v>40100</v>
       </c>
       <c r="E83" s="3">
-        <v>57900</v>
+        <v>35200</v>
       </c>
       <c r="F83" s="3">
-        <v>52500</v>
+        <v>32700</v>
       </c>
       <c r="G83" s="3">
-        <v>47200</v>
+        <v>29800</v>
       </c>
       <c r="H83" s="3">
-        <v>42300</v>
+        <v>27600</v>
       </c>
       <c r="I83" s="3">
-        <v>39800</v>
+        <v>26100</v>
       </c>
       <c r="J83" s="3">
+        <v>24700</v>
+      </c>
+      <c r="K83" s="3">
         <v>36900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>34700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>33200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>31900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>30600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>29000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>27800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>19500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>18300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>17000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>15900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>14900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>14400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>12300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>11600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>11000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>10400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>10600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>9400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>9000</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6580,8 +6782,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6666,8 +6871,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6752,8 +6960,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6838,8 +7049,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6924,94 +7138,100 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-94200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-80100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-65600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-42800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-12200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-13200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-169300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-67600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-103500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-70200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-92100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-62400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-36200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-60800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-49900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-29700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-18900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-24800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-58100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-95700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-18800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-31300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-24400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>13700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-4700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-1300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-19200</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7042,94 +7262,98 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-464800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-465700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-398800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-517500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-567000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-458900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-289300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-230700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-257100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-242300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-138200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-210500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-107700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-118900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-117500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-138500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-165500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-133100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-141200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-131600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-134400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-95900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-68900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-68400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-60200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-63100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-61000</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7214,8 +7438,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7300,94 +7527,100 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-469200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-424800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-458700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-652900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-717800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-649600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-524300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-530200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-557400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-536300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-357700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-394000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-338000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-283000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-226200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-235200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-236700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-173300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-184300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-178600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-172300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-124700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-92700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-89000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-88000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-87500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-84300</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7418,31 +7651,32 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -7504,8 +7738,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7590,8 +7827,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7676,8 +7916,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7762,117 +8005,123 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>407000</v>
+      </c>
+      <c r="E100" s="3">
         <v>647800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>517400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>465000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1049300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>647900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>568900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>603600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>836800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>645500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>382800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>328000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>425300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>549400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>161700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>431100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>282800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>213300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>261400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>315400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>200900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>176200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>109400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>62500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>110200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>47200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>145800</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -7934,90 +8183,96 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-156400</v>
+      </c>
+      <c r="E102" s="3">
         <v>142900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-6900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-230700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>319200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-14900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-124800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>5700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>176000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>39000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-67000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-128400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>51200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>205600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-114400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>166200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>27300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>15200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>18900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>41000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>9800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>20200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-7800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-12900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>17500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-41700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>42300</v>
       </c>
-      <c r="AD102" s="3" t="s">
+      <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NOVA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NOVA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="92">
   <si>
     <t>NOVA</t>
   </si>
@@ -656,404 +656,416 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>224100</v>
+      </c>
+      <c r="E8" s="3">
         <v>235300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>219600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>160900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>194200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>198400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>166400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>161700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>195600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>149400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>147000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>65700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>65000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>68900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>66600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>41300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>38000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>50200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>42800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>29800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>33600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>36600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>34600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>26700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>25200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>30400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>29000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>19800</v>
       </c>
-      <c r="AE8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>185000</v>
+      </c>
+      <c r="E9" s="3">
         <v>157300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>83900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>76500</v>
       </c>
-      <c r="G9" s="3">
-        <v>97200</v>
-      </c>
       <c r="H9" s="3">
+        <v>182400</v>
+      </c>
+      <c r="I9" s="3">
         <v>134100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>87800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>81100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>134300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>81100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>82100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>29500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>29100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>27000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>23500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>18600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>17700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>16500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>16900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>14000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>13700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>12100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>11300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>10300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>9800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>10000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>8700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>8300</v>
       </c>
-      <c r="AE9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>39200</v>
+      </c>
+      <c r="E10" s="3">
         <v>78000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>135700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>84400</v>
       </c>
-      <c r="G10" s="3">
-        <v>97000</v>
-      </c>
       <c r="H10" s="3">
+        <v>11800</v>
+      </c>
+      <c r="I10" s="3">
         <v>64300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>78600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>80600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>61300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>68300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>64900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>36200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>35900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>41900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>43100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>22700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>20300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>33700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>25900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>15800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>19900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>24500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>23300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>16400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>15400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>20400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>20300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>11500</v>
       </c>
-      <c r="AE10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1085,8 +1097,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1174,8 +1187,11 @@
       <c r="AE12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1263,124 +1279,130 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>-44500</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>9400</v>
       </c>
-      <c r="G14" s="3">
-        <v>39800</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
+      <c r="H14" s="3">
+        <v>-7600</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>-100</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>1200</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>9800</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T14" s="3">
         <v>92100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>50700</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
       </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>10600</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>3</v>
+      <c r="AD14" s="3">
+        <v>0</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>71900</v>
+      </c>
+      <c r="E15" s="3">
         <v>68400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>46400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>42200</v>
       </c>
-      <c r="G15" s="3">
-        <v>38000</v>
-      </c>
       <c r="H15" s="3">
+        <v>54000</v>
+      </c>
+      <c r="I15" s="3">
         <v>48400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>30300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>28200</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1441,8 +1463,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1471,186 +1496,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>326500</v>
+      </c>
+      <c r="E17" s="3">
         <v>287800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>278500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>235700</v>
       </c>
-      <c r="G17" s="3">
-        <v>254200</v>
-      </c>
       <c r="H17" s="3">
+        <v>301500</v>
+      </c>
+      <c r="I17" s="3">
         <v>236600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>226100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>210600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>212400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>177100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>149700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>99900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>74100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>77100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>90700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>64600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>148100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>99200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>47900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>44100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>42800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>42500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>48000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>31200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>37600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>27000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>26500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>26900</v>
       </c>
-      <c r="AE17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-102400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-52500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-58900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-74800</v>
       </c>
-      <c r="G18" s="3">
-        <v>-60000</v>
-      </c>
       <c r="H18" s="3">
+        <v>-107400</v>
+      </c>
+      <c r="I18" s="3">
         <v>-38200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-59800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-48900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-16800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-27700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-34200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-9100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-8200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-24100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-23300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-110100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-49000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-5100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-14300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-9200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-5900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-13400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-12400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>3400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-7100</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1682,394 +1714,407 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" s="3">
+      <c r="D20" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3">
         <v>4900</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-3100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>3200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>22100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>16200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>13500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>12100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>9500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>8900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>8000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>7300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>8000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>5900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>6900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>4600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>3600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>3100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2400</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
         <v>0</v>
       </c>
       <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>1800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1400</v>
       </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-23100</v>
+      </c>
+      <c r="E21" s="3">
         <v>15900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-17400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-32600</v>
       </c>
-      <c r="G21" s="3">
-        <v>-18900</v>
-      </c>
       <c r="H21" s="3">
+        <v>-50300</v>
+      </c>
+      <c r="I21" s="3">
         <v>9700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-32600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-20900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>42200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>23200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>43900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>9800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>31000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>29700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>11700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>3500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-83800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-26200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>17700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>5300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>8800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>9600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>6500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>15800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>13300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1800</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>102500</v>
+      </c>
+      <c r="E22" s="3">
         <v>182500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>121500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>84600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>171800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>57600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>56900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>85600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>71500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>20800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>24600</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
       <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
         <v>31500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>26600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>50100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>8100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>26800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>30000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>30500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>67300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>8200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>31600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>38900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>31000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>26700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>11800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>13100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>6300</v>
       </c>
-      <c r="AE22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-112800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-196500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-150000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-133100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-234200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-65800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-93600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-109800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-66200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-32300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-13800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-22100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-31100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-25900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-66300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-24100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-128800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-73100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-28700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-77000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-13800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-34400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-49800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-35500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-39100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-6600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-9200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-13400</v>
       </c>
-      <c r="AE23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E24" s="3">
         <v>-46100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-70300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-43000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-9300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>7200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3900</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
@@ -2077,26 +2122,26 @@
         <v>0</v>
       </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
+      <c r="S24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>200</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
         <v>0</v>
       </c>
@@ -2127,8 +2172,11 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2216,186 +2264,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-127700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-150300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-79700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-90100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-234800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-56500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-100800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-110300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-70100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-32300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-13800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-22100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-31300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-25900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-66300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-24100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-128800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-73300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-28700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-77000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-13800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-34400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-49800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-35500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-39100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-6600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-9200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-13400</v>
       </c>
-      <c r="AE26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-142300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-122600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-33100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-70000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-187600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-63100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-86100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-81100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-29000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-64500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-41100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-35100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-14200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-27500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-63400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-33000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-91800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-64200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-25300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-71100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-17500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-37600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-63300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-50700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-53000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-17900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-23300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-41700</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2483,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2572,8 +2632,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2661,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2750,186 +2816,195 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E32" s="3">
+      <c r="D32" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3">
         <v>-4900</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>3100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-3200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-22100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-16200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-13500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-12100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-9500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-8900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-8000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-7300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-8000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-5900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-6900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-4600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-3600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
         <v>0</v>
       </c>
       <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-142300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-122600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-33100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-70000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-187600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-63100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-86100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-81100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-29000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-64500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-41100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-35100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-14200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-27500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-63400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-33000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-91800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-64200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-25300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-71100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-17500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-37600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-63300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-50700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-53000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-17900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-23300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-41700</v>
       </c>
-      <c r="AE33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3017,191 +3092,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-142300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-122600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-33100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-70000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-187600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-63100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-86100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-81100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-29000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-64500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-41100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-35100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-14200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-27500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-63400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-33000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-91800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-64200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-25300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-71100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-17500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-37600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-63300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-50700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-53000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-17900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-23300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-41700</v>
       </c>
-      <c r="AE35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3233,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3266,83 +3351,84 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>211200</v>
+      </c>
+      <c r="E41" s="3">
         <v>208900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>253200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>231700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>212800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>467900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>187300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>210900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>360300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>412600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>208100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>208500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>243100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>408200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>368600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>150900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>209900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>84600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>102300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>73400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>83500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>51000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>58800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>43900</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3355,35 +3441,38 @@
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>7400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>7500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>7300</v>
       </c>
-      <c r="G42" s="3">
-        <v>7500</v>
-      </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>7600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>7800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>8000</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -3444,83 +3533,86 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>565700</v>
+      </c>
+      <c r="E43" s="3">
         <v>512500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>535100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>390100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>478300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>320900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>304200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>353100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>358800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>289900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>227800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>145300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>139200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>95400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>78000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>63200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>56500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>46100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>37100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>35400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>31600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>29000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>26900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>20800</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3533,83 +3625,86 @@
       <c r="AE43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>126700</v>
+      </c>
+      <c r="E44" s="3">
         <v>136600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>132100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>130800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>148600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>137700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>179200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>182900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>152100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>186600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>150700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>150500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>128000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>134900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>128000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>107700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>102600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>111000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>120800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>115100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>43700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>17100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>16500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>15800</v>
       </c>
-      <c r="AA44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3622,83 +3717,86 @@
       <c r="AE44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E45" s="3">
         <v>100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>800</v>
       </c>
-      <c r="G45" s="3">
-        <v>900</v>
-      </c>
       <c r="H45" s="3">
-        <v>700</v>
+        <v>8400</v>
       </c>
       <c r="I45" s="3">
         <v>700</v>
       </c>
       <c r="J45" s="3">
+        <v>700</v>
+      </c>
+      <c r="K45" s="3">
         <v>100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>77200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>48300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>84100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>58300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>105500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>79300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>65100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>55000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>87700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>67700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>26600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>56000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>115500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>29300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>6800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>5500</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3711,83 +3809,86 @@
       <c r="AE45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1027500</v>
+      </c>
+      <c r="E46" s="3">
         <v>914600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1053200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>817400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>936200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>993900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>746800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>828100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>948400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>937300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>670700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>562600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>615700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>717700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>639700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>376800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>456700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>309400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>286800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>280000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>274300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>126400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>109000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>86000</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3800,83 +3901,86 @@
       <c r="AE46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E47" s="3">
         <v>63300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>86800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>114800</v>
       </c>
-      <c r="G47" s="3">
-        <v>117300</v>
-      </c>
       <c r="H47" s="3">
+        <v>55500</v>
+      </c>
+      <c r="I47" s="3">
         <v>186300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>182800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>196600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2466100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2072300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1736600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1450000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1204100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>962500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>773500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>622900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>513400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>428600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>379000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>338500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>298000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>255100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>223600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>197800</v>
       </c>
-      <c r="AA47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3889,83 +3993,86 @@
       <c r="AE47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7335200</v>
+      </c>
+      <c r="E48" s="3">
         <v>6884100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6405800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5974800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5577600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5065200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4464400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4010500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3802000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3554800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3306100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3075200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2928300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2748300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2602300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2455000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2332300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2181700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2015300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1894000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1754700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1629900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1499900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1399300</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3978,56 +4085,59 @@
       <c r="AE48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>105200</v>
+      </c>
+      <c r="E49" s="3">
         <v>112300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>119400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>126500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>134100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>154300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>161400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>168600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>175700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>182300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>189400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>196600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>203700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>210900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>204200</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4043,8 +4153,8 @@
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X49" s="3">
-        <v>0</v>
+      <c r="X49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y49" s="3">
         <v>0</v>
@@ -4067,8 +4177,11 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4156,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4245,83 +4361,86 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>943400</v>
+      </c>
+      <c r="E52" s="3">
         <v>775200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>847000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>701000</v>
       </c>
-      <c r="G52" s="3">
-        <v>617700</v>
-      </c>
       <c r="H52" s="3">
+        <v>901600</v>
+      </c>
+      <c r="I52" s="3">
         <v>604400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>517600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>451600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>944700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>903100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>785000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>644200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>552500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>421100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>346500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>301900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>285200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>234600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>186500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>169700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>160000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>138400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>120100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>86400</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4334,8 +4453,11 @@
       <c r="AE52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4423,83 +4545,86 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>13353700</v>
+      </c>
+      <c r="E54" s="3">
         <v>12882300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>12560700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>11815600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>11341000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>10785300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>9606800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8902200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8336900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7649700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6687800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5928500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5504200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5060400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4566100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3756600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3587600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3154300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2867600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2682200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2487100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2149800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1952700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1769500</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4512,8 +4637,11 @@
       <c r="AE54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4545,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4578,83 +4707,84 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>699400</v>
+      </c>
+      <c r="E57" s="3">
         <v>484300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>504100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>374900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>355800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>194600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>138800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>123500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>116100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>94600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>82500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>72500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>55000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>53600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>40000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>33900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>39900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>29300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>27600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>59700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>36200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>40300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>45100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>34900</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4667,83 +4797,86 @@
       <c r="AE57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>334800</v>
+      </c>
+      <c r="E58" s="3">
         <v>330100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>337700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>498000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>487700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>474100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>245400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>212600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>215200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>191900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>166600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>155800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>130500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>119300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>128900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>116300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>111000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>109700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>114100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>100700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>102500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>59400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>75900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>51500</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4756,83 +4889,86 @@
       <c r="AE58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>84500</v>
+      </c>
+      <c r="E59" s="3">
         <v>69800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>72500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>76000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>61800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>56900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>47700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>43400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>210600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>171600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>138700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>117400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>125400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>90300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>70200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>67100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>60000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>46500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>48000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>30500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>56300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>31400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>37600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>23700</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4845,83 +4981,86 @@
       <c r="AE59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1323800</v>
+      </c>
+      <c r="E60" s="3">
         <v>1059000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1087600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1102400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1095300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>868800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>580500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>528000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>541900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>458100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>387700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>345600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>310900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>263200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>239100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>217300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>210900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>185500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>189800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>190900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>195000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>131200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>158600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>110100</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4934,83 +5073,86 @@
       <c r="AE60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8151200</v>
+      </c>
+      <c r="E61" s="3">
         <v>7968800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7659000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7288800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7046400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6726500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6139800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5637400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5195700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4808100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3986800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3462600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3136700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2933200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2593900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1994900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1924900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1795000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1628700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1511600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1346400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1116400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1152900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1016400</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
       <c r="AB61" s="3">
         <v>0</v>
       </c>
@@ -5023,83 +5165,86 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>149400</v>
+      </c>
+      <c r="E62" s="3">
         <v>141800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>128900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>121200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>130200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>124000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>121200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>104300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>711800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>630200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>535600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>467600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>435000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>371800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>320600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>183400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>171200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>162400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>149200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>145300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>127400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>119100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>92000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>75600</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5112,8 +5257,11 @@
       <c r="AE62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5201,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5290,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5379,83 +5533,86 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10668600</v>
+      </c>
+      <c r="E66" s="3">
         <v>10198900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9886000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9493800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>9212100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>8583400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7618700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6955400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7063800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6403300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5387400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4694900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4314700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3965300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3499400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2733700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2635900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2431700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2205900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2090200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1841100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1523200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1511100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1296100</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5468,8 +5625,11 @@
       <c r="AE66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5501,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5590,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5679,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5748,14 +5915,14 @@
         <v>0</v>
       </c>
       <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="3">
         <v>600</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AA70" s="3">
         <v>1400</v>
       </c>
-      <c r="AA70" s="3">
-        <v>0</v>
-      </c>
       <c r="AB70" s="3">
         <v>0</v>
       </c>
@@ -5768,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5857,83 +6027,86 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>46600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-32400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-163000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-228600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-191500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-272200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-367000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-364800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-387100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-377200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-423500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-459700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-505800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-529900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-524500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-531000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-476100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-426500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-418600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-361800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-365400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-347200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-314700</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5946,8 +6119,11 @@
       <c r="AE72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6035,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6124,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6213,83 +6395,86 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1831600</v>
+      </c>
+      <c r="E76" s="3">
         <v>1778900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1743100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1604000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1526900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1557900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1389800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1278800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1273100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1246400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1300400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1233600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1189500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1095200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1066700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1022900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>951700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>722600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>661700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>592000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>645900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>626600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>441000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>472000</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6302,8 +6487,11 @@
       <c r="AE76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6391,191 +6579,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-142300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-122600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-33100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-70000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-187600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-63100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-86100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-81100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-29000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-64500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-41100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-35100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-14200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-27500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-63400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-33000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-91800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-64200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-25300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-71100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-17500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-37600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-63300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-50700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-53000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-17900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-23300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-41700</v>
       </c>
-      <c r="AE81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6607,97 +6804,101 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>45400</v>
+      </c>
+      <c r="E83" s="3">
         <v>40100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>35200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>32700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>29800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>27600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>26100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>24700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>36900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>34700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>33200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>31900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>30600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>29000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>27800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>19500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>18300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>17000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>15900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>14900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>14400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>12300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>11600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>11000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>10400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>10600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>9400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>9000</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6785,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6874,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6963,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7052,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7141,97 +7354,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-70900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-94200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-80100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-65600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-42800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-12200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-13200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-169300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-67600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-103500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-70200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-92100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-62400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-36200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-60800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-49900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-29700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-18900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-24800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-58100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-95700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-18800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-31300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-24400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>13700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-4700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-19200</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7263,97 +7482,101 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-313600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-464800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-465700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-398800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-517500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-567000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-458900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-289300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-230700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-257100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-242300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-138200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-210500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-107700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-118900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-117500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-138500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-165500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-133100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-141200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-131600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-134400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-95900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-68900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-68400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-60200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-63100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-61000</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7441,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7530,97 +7756,103 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-263100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-469200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-424800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-458700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-652900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-717800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-649600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-524300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-530200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-557400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-536300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-357700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-394000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-338000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-283000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-226200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-235200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-236700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-173300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-184300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-178600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-172300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-124700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-92700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-89000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-88000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-87500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-84300</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7652,8 +7884,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7678,8 +7911,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -7741,8 +7974,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7830,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7919,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8008,97 +8250,103 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>408100</v>
+      </c>
+      <c r="E100" s="3">
         <v>407000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>647800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>517400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>465000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1049300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>647900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>568900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>603600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>836800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>645500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>382800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>328000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>425300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>549400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>161700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>431100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>282800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>213300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>261400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>315400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>200900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>176200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>109400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>62500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>110200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>47200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>145800</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8123,8 +8371,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -8186,93 +8434,99 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>74200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-156400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>142900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-6900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-230700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>319200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-14900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-124800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>5700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>176000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>39000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-67000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-128400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>51200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>205600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-114400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>166200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>27300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>15200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>18900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>41000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>9800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>20200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-7800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-12900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>17500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-41700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>42300</v>
       </c>
-      <c r="AE102" s="3" t="s">
+      <c r="AF102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
